--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
   </si>
   <si>
     <t xml:space="preserve">Ce ConceptMap présente deux groupes de mapping : 
- - Mapping 1 : entre le modèle métier \"auteur\" et l'élément CDA \"author\"
+ - Mapping 1 : entre le modèle métier \"Auteur\" et l'élément CDA \"author\"
  - Mapping 2 : entre l'élément CDA \"author\" et l'élément FHIR \"Composition.author\" </t>
   </si>
   <si>
@@ -105,16 +105,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Auteur</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-author</t>
-  </si>
-  <si>
-    <t>Auteur</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-author</t>
+  </si>
+  <si>
+    <t>FRLMAuteur</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -123,25 +123,25 @@
     <t>author</t>
   </si>
   <si>
-    <t>Auteur.roleFonctionnel</t>
+    <t>FRLMAuteur.roleFonctionnel</t>
   </si>
   <si>
     <t>author.functionCode</t>
   </si>
   <si>
-    <t>Auteur.horodatageParticipation</t>
+    <t>FRLMAuteur.horodatageParticipation</t>
   </si>
   <si>
     <t>author.time</t>
   </si>
   <si>
-    <t>Auteur.PersonneStructure</t>
+    <t>FRLMAuteur.FRLMPersonneStructure</t>
   </si>
   <si>
     <t>author.assignedAuthor</t>
   </si>
   <si>
-    <t>Auteur.SystemeStructureAuteur</t>
+    <t>FRLMAuteur.FRLMSystemeStructureAuteur</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingAuteurCDAFHIR.xlsx
+++ b/main/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
